--- a/Speciallægeloft/speciallægeloft_data/Region_Hovedstaden.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Region_Hovedstaden.xlsx
@@ -19,42 +19,42 @@
     <t/>
   </si>
   <si>
+    <t>dec 2024</t>
+  </si>
+  <si>
+    <t>jan 2025</t>
+  </si>
+  <si>
+    <t>feb 2025</t>
+  </si>
+  <si>
+    <t>mar 2025</t>
+  </si>
+  <si>
+    <t>apr 2025</t>
+  </si>
+  <si>
+    <t>maj 2025</t>
+  </si>
+  <si>
+    <t>jun 2025</t>
+  </si>
+  <si>
+    <t>jul 2025</t>
+  </si>
+  <si>
+    <t>aug 2025</t>
+  </si>
+  <si>
+    <t>sep 2025</t>
+  </si>
+  <si>
+    <t>okt 2025</t>
+  </si>
+  <si>
     <t>nov 2025</t>
   </si>
   <si>
-    <t>okt 2025</t>
-  </si>
-  <si>
-    <t>sep 2025</t>
-  </si>
-  <si>
-    <t>aug 2025</t>
-  </si>
-  <si>
-    <t>jul 2025</t>
-  </si>
-  <si>
-    <t>jun 2025</t>
-  </si>
-  <si>
-    <t>maj 2025</t>
-  </si>
-  <si>
-    <t>apr 2025</t>
-  </si>
-  <si>
-    <t>mar 2025</t>
-  </si>
-  <si>
-    <t>feb 2025</t>
-  </si>
-  <si>
-    <t>jan 2025</t>
-  </si>
-  <si>
-    <t>dec 2024</t>
-  </si>
-  <si>
     <t>Organisation niveau 1</t>
   </si>
   <si>
@@ -82,10 +82,10 @@
     <t>Lokale Løndata</t>
   </si>
   <si>
-    <t>Datasæt 11 2025</t>
-  </si>
-  <si>
-    <t>Kørsel 15.4.2026 13.33.51</t>
+    <t>Datasæt 12 2024</t>
+  </si>
+  <si>
+    <t>Kørsel 15.4.2026 14.35.13</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -702,19 +702,19 @@
         <v>16</v>
       </c>
       <c r="B4" s="6">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C4" s="6">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D4" s="6">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E4" s="6">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F4" s="6">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G4" s="6">
         <v>82</v>
@@ -723,19 +723,19 @@
         <v>82</v>
       </c>
       <c r="I4" s="6">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J4" s="6">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K4" s="6">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="L4" s="6">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="M4" s="6">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -743,40 +743,40 @@
         <v>17</v>
       </c>
       <c r="B5" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="8">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8">
         <v>7</v>
-      </c>
-      <c r="E5" s="8">
-        <v>8</v>
       </c>
       <c r="F5" s="8">
         <v>7</v>
       </c>
       <c r="G5" s="8">
+        <v>8</v>
+      </c>
+      <c r="H5" s="8">
         <v>7</v>
-      </c>
-      <c r="H5" s="8">
-        <v>8</v>
       </c>
       <c r="I5" s="8">
         <v>7</v>
       </c>
       <c r="J5" s="8">
+        <v>8</v>
+      </c>
+      <c r="K5" s="8">
         <v>7</v>
       </c>
-      <c r="K5" s="8">
-        <v>8</v>
-      </c>
       <c r="L5" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -784,13 +784,13 @@
         <v>18</v>
       </c>
       <c r="B6" s="6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C6" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" s="6">
         <v>36</v>
@@ -811,13 +811,13 @@
         <v>36</v>
       </c>
       <c r="K6" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -825,40 +825,40 @@
         <v>19</v>
       </c>
       <c r="B7" s="8">
+        <v>36</v>
+      </c>
+      <c r="C7" s="8">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8">
+        <v>35</v>
+      </c>
+      <c r="E7" s="8">
+        <v>37</v>
+      </c>
+      <c r="F7" s="8">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8">
+        <v>38</v>
+      </c>
+      <c r="H7" s="8">
+        <v>39</v>
+      </c>
+      <c r="I7" s="8">
+        <v>39</v>
+      </c>
+      <c r="J7" s="8">
+        <v>40</v>
+      </c>
+      <c r="K7" s="8">
         <v>43</v>
       </c>
-      <c r="C7" s="8">
+      <c r="L7" s="8">
         <v>43</v>
       </c>
-      <c r="D7" s="8">
+      <c r="M7" s="8">
         <v>43</v>
-      </c>
-      <c r="E7" s="8">
-        <v>40</v>
-      </c>
-      <c r="F7" s="8">
-        <v>39</v>
-      </c>
-      <c r="G7" s="8">
-        <v>39</v>
-      </c>
-      <c r="H7" s="8">
-        <v>38</v>
-      </c>
-      <c r="I7" s="8">
-        <v>37</v>
-      </c>
-      <c r="J7" s="8">
-        <v>37</v>
-      </c>
-      <c r="K7" s="8">
-        <v>35</v>
-      </c>
-      <c r="L7" s="8">
-        <v>36</v>
-      </c>
-      <c r="M7" s="8">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
